--- a/docs/PRAP_NewApp_Development_Plan_v1.0.xlsx
+++ b/docs/PRAP_NewApp_Development_Plan_v1.0.xlsx
@@ -11640,12 +11640,12 @@
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Specification sheet 'Storage'</t>
+          <t>Specification sheets 03, 04</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Complete - issued for review</t>
         </is>
       </c>
     </row>
@@ -11662,17 +11662,17 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Specify the desktop shell: window, menus, dialogs, recent files, drag-and-drop, About.</t>
+          <t>Specify the desktop shell: window, menus, dialogs, recent files, drag-and-drop, About; and user identity.</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Specification sheet 'Shell'</t>
+          <t>Specification sheets 05, 08</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Complete - issued for review</t>
         </is>
       </c>
     </row>
@@ -11689,17 +11689,17 @@
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>Specify save safety, version retention, journalling and recovery.</t>
+          <t>Specify save safety, version retention, journalling and recovery; and the write claim.</t>
         </is>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>Specification sheet 'Persistence'</t>
+          <t>Specification sheets 06, 07</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Complete - issued for review</t>
         </is>
       </c>
     </row>
@@ -11716,17 +11716,17 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Specify the re-import difference dialog.</t>
+          <t>Specify the re-import difference report, the look-without-a-workspace path, and protected files.</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Specification sheet 'Import'</t>
+          <t>Specification sheet 09</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Complete - issued for review</t>
         </is>
       </c>
     </row>
@@ -11743,17 +11743,17 @@
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Specify packaging, deployment and update.</t>
+          <t>Specify packaging, deployment, the folder layout, data resolution and update.</t>
         </is>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>Specification sheet 'Deployment'</t>
+          <t>Specification sheet 10</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Complete - issued for review</t>
         </is>
       </c>
     </row>
@@ -11770,17 +11770,17 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Traceability matrix: every NR-id to a specification section.</t>
+          <t>Traceability matrix: every NR-id to a specification section, read from the plan rather than re-typed.</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>Specification sheet 'Traceability'</t>
+          <t>Specification sheet 11</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Complete - 69/69 specified</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Pending you</t>
         </is>
       </c>
     </row>
